--- a/public/modeles/bilan-promoteur-exemple-fictif.xlsx
+++ b/public/modeles/bilan-promoteur-exemple-fictif.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -526,74 +526,105 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aucun taux ni prix de ce fichier n'est une référence de marché : ce sont des valeurs d'exemple.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Onglet « Compte à rebours » : à partir d'une marge cible, calcule la charge foncière admissible</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>et le prix maximal du terrain hors frais d'acquisition.</t>
+          <t>Onglet « Compte à rebours » : à partir d'une marge cible, calcule la charge foncière admissible</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>et le prix maximal du terrain hors frais d'acquisition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Onglet « Bilan direct » : à partir d'un prix de terrain négocié, calcule la marge obtenue.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Simplifications assumées : montants hors taxes ; frais financiers forfaitaires en % du chiffre</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>d'affaires (sans échéancier) ; taxe d'aménagement et participations saisies en montant ;</t>
+          <t>Simplifications assumées : montants hors taxes ; frais financiers forfaitaires en % du chiffre</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>d'affaires (sans échéancier) ; taxe d'aménagement et participations saisies en montant ;</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>aucune fiscalité propre à votre structure.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Ce fichier est une aide au raisonnement. Ce n'est ni un certificat d'urbanisme, ni un avis</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juridique, fiscal ou financier. La surface de plancher réellement constructible se confirme</t>
+          <t>Ce fichier est une aide au raisonnement. Ce n'est ni un certificat d'urbanisme, ni un avis</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>juridique, fiscal ou financier. La surface de plancher réellement constructible se confirme</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>auprès du service urbanisme de la commune ; les coûts, par des devis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Postes et formules : ceux de la page https://fonciable.fr/bilan-promoteur (méthode du compte à rebours).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Dans l'application Fonciable, le bilan part des données publiques de la parcelle et d'hypothèses</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>de départ que vous ajustez : https://app.fonciable.fr</t>
         </is>
       </c>
     </row>
@@ -608,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -667,7 +698,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
+          <t>Exemple fictif à remplacer</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -687,7 +718,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
+          <t>Exemple fictif à remplacer</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -737,7 +768,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
+          <t>Exemple fictif à remplacer</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -749,7 +780,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ventes de logements HT</t>
+          <t>Ventes de logements et de locaux HT</t>
         </is>
       </c>
       <c r="B11" s="12">
@@ -766,7 +797,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Autres recettes HT (stationnement, locaux…)</t>
+          <t>Places de stationnement et autres recettes HT</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
@@ -774,10 +805,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
+          <t>Exemple fictif à remplacer</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Montant total ; 0 si aucune.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -820,7 +855,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
+          <t>Exemple fictif à remplacer</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -832,7 +867,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Travaux</t>
+          <t>Travaux de construction</t>
         </is>
       </c>
       <c r="B17" s="12">
@@ -849,31 +884,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Honoraires techniques (% des travaux)</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>0.1</v>
+          <t>Sous-sols et adaptation au terrain (pente, fondations)</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
+          <t>Exemple fictif à remplacer</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Architecte, bureaux d'études, contrôle…</t>
+          <t>Montant total ; 0 si sans objet.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Honoraires techniques</t>
+          <t>Total des travaux</t>
         </is>
       </c>
       <c r="B19" s="12">
-        <f>B17*B18</f>
+        <f>B17+B18</f>
         <v/>
       </c>
       <c r="C19" t="inlineStr">
@@ -886,27 +921,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Assurances (% des travaux)</t>
+          <t>Honoraires techniques (% des travaux)</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
+          <t>Exemple fictif à remplacer</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Architecte, bureaux d'études, géomètre, contrôle…</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Assurances</t>
+          <t>Honoraires techniques</t>
         </is>
       </c>
       <c r="B21" s="12">
-        <f>B17*B20</f>
+        <f>B19*B20</f>
         <v/>
       </c>
       <c r="C21" t="inlineStr">
@@ -919,80 +958,88 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Aléas (% des travaux)</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>0.03</v>
+          <t>Taxe d'aménagement, archéologie préventive, participations</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>80000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr"/>
+          <t>Exemple fictif à remplacer</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Montant à calculer pour la commune.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aléas</t>
-        </is>
-      </c>
-      <c r="B23" s="12">
-        <f>B17*B22</f>
-        <v/>
+          <t>Assurances (% des travaux)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>0.02</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Calcul</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
+          <t>Exemple fictif à remplacer</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Dommages-ouvrage notamment.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Taxe d'aménagement et participations</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="n">
-        <v>80000</v>
+          <t>Assurances</t>
+        </is>
+      </c>
+      <c r="B24" s="12">
+        <f>B19*B23</f>
+        <v/>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Montant à calculer pour la commune.</t>
-        </is>
-      </c>
+          <t>Calcul</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Frais de commercialisation (% du CA)</t>
+          <t>Aléas (% des travaux)</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr"/>
+          <t>Exemple fictif à remplacer</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Provision pour imprévus.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Frais de commercialisation</t>
+          <t>Aléas</t>
         </is>
       </c>
       <c r="B26" s="12">
-        <f>B13*B25</f>
+        <f>B19*B25</f>
         <v/>
       </c>
       <c r="C26" t="inlineStr">
@@ -1005,27 +1052,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Frais financiers (% du CA)</t>
+          <t>Frais de commercialisation (% du CA)</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>0.025</v>
+        <v>0.04</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
+          <t>Exemple fictif à remplacer</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Forfait simplifié, sans échéancier.</t>
+          <t>Honoraires de vente, publicité…</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Frais financiers</t>
+          <t>Frais de commercialisation</t>
         </is>
       </c>
       <c r="B28" s="12">
@@ -1040,121 +1087,117 @@
       <c r="D28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Frais financiers (% du CA)</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Exemple fictif à remplacer</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Forfait simplifié, sans échéancier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Frais financiers</t>
+        </is>
+      </c>
+      <c r="B30" s="12">
+        <f>B13*B29</f>
+        <v/>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Calcul</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Total des dépenses hors foncier</t>
         </is>
       </c>
-      <c r="B29" s="14">
-        <f>B17+B19+B21+B23+B24+B26+B28</f>
-        <v/>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Calcul</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="B31" s="14">
+        <f>B19+B21+B22+B24+B26+B28+B30</f>
+        <v/>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Calcul</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Marge et foncier</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Marge cible (% du CA HT)</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n">
+      <c r="B34" s="8" t="n">
         <v>0.12</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Hypothèse fictive</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Exemple fictif à remplacer</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>Objectif de l'opérateur.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Marge cible</t>
-        </is>
-      </c>
-      <c r="B33" s="12">
-        <f>B13*B32</f>
-        <v/>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Calcul</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Charge foncière admissible (frais d'acquisition inclus)</t>
-        </is>
-      </c>
-      <c r="B34" s="14">
-        <f>B13-B33-B29</f>
-        <v/>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Calcul</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>CA HT − marge − dépenses hors foncier.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Frais d'acquisition (% du prix du terrain)</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n">
-        <v>0.075</v>
+          <t>Marge cible</t>
+        </is>
+      </c>
+      <c r="B35" s="12">
+        <f>B13*B34</f>
+        <v/>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Notaire, droits : à confirmer.</t>
-        </is>
-      </c>
+          <t>Calcul</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Prix maximal du terrain hors frais</t>
+          <t>Charge foncière admissible (frais d'acquisition inclus)</t>
         </is>
       </c>
       <c r="B36" s="14">
-        <f>B34/(1+B35)</f>
+        <f>B13-B35-B31</f>
         <v/>
       </c>
       <c r="C36" t="inlineStr">
@@ -1164,43 +1207,88 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Base de l'offre au propriétaire.</t>
+          <t>CA HT − marge cible − dépenses hors foncier.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Frais d'acquisition (% du prix du terrain)</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Exemple fictif à remplacer</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Notaire, droits : à confirmer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Prix maximal du terrain hors frais</t>
+        </is>
+      </c>
+      <c r="B38" s="14">
+        <f>B36/(1+B37)</f>
+        <v/>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Calcul</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Charge foncière ÷ (1 + frais). Base de l'offre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Incidence foncière par m² de SDP</t>
         </is>
       </c>
-      <c r="B37" s="15">
-        <f>B34/B5</f>
-        <v/>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Calcul</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="B39" s="15">
+        <f>B36/B5</f>
+        <v/>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Calcul</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Charge foncière ÷ SDP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Part du foncier dans le CA HT</t>
         </is>
       </c>
-      <c r="B38" s="16">
-        <f>B34/B13</f>
-        <v/>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Calcul</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr"/>
+      <c r="B40" s="16">
+        <f>B36/B13</f>
+        <v/>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Calcul</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1285,7 +1373,7 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>'Compte à rebours'!B29</f>
+        <f>'Compte à rebours'!B31</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr">
@@ -1302,7 +1390,7 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>'Compte à rebours'!B35</f>
+        <f>'Compte à rebours'!B37</f>
         <v/>
       </c>
       <c r="C7" t="inlineStr">
@@ -1336,7 +1424,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hypothèse fictive</t>
+          <t>Exemple fictif à remplacer</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
